--- a/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_district_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_district_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03312016298902989</v>
+        <v>0.05240593133581765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -693,19 +693,19 @@
         <v>1.105305255087362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0331201629890299</v>
+        <v>0.05240602355202012</v>
       </c>
       <c r="G7" t="n">
         <v>1.105305255087362</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0331234000354338</v>
+        <v>0.05237990773142319</v>
       </c>
       <c r="I7" t="n">
         <v>0.2970002231424656</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0331201629890299</v>
+        <v>0.0523799077314232</v>
       </c>
       <c r="K7" t="n">
         <v>0.2970002231424656</v>
@@ -716,7 +716,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03341991435575395</v>
+        <v>0.05694508891764707</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -730,19 +730,19 @@
         <v>1.105305255087362</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03341991435575396</v>
+        <v>0.05694508891764706</v>
       </c>
       <c r="G8" t="n">
         <v>1.105305255087362</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03341991435575396</v>
+        <v>0.05688373348235295</v>
       </c>
       <c r="I8" t="n">
         <v>0.4475215747426022</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03341991435575396</v>
+        <v>0.05694508891764706</v>
       </c>
       <c r="K8" t="n">
         <v>0.4475215747426022</v>
@@ -753,7 +753,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03373117671399527</v>
+        <v>0.05694508891764708</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -767,19 +767,19 @@
         <v>1.105305255087362</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03373117671399527</v>
+        <v>0.05710372246556973</v>
       </c>
       <c r="G9" t="n">
         <v>1.105305255087362</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03373117671399527</v>
+        <v>0.05688373348235295</v>
       </c>
       <c r="I9" t="n">
         <v>0.5364487790789384</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03373117671399527</v>
+        <v>0.05694508891764706</v>
       </c>
       <c r="K9" t="n">
         <v>0.5364487790789384</v>
@@ -790,7 +790,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03367501954145533</v>
+        <v>0.05694508891764708</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
         <v>1.105305255087362</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03356411722597039</v>
+        <v>0.05710372246556974</v>
       </c>
       <c r="G10" t="n">
         <v>1.105305255087362</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03373117671399527</v>
+        <v>0.05688373348235294</v>
       </c>
       <c r="I10" t="n">
         <v>0.5945233624365646</v>
       </c>
       <c r="J10" t="n">
-        <v>0.03373117671399527</v>
+        <v>0.05694508891764706</v>
       </c>
       <c r="K10" t="n">
         <v>0.5945233624365646</v>
@@ -827,7 +827,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03368034538024912</v>
+        <v>0.05865504987026251</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -841,19 +841,19 @@
         <v>1.105305255087362</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03350819836805017</v>
+        <v>0.05860209760840105</v>
       </c>
       <c r="G11" t="n">
         <v>1.105305255087362</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03409657258695716</v>
+        <v>0.05728816702997307</v>
       </c>
       <c r="I11" t="n">
         <v>0.6352278808517205</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03398486794736134</v>
+        <v>0.05733784613978269</v>
       </c>
       <c r="K11" t="n">
         <v>0.6352278808517205</v>
@@ -1042,746 +1042,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.001394069274389265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.001394069274389266</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.001394217253653444</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.001394069274389266</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.867646821589003</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.001441572793246098</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.001441572793246097</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.001445057298303677</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.001441572793246098</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.867646821589003</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.001583435552264311</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.001583435552264311</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.00158692005732189</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.00158343555226431</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.867646821589003</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.001599787670037673</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.001609007269720386</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.001615736840771982</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.001615736840771982</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.867646821589003</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.001599787670037673</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.001611563560368167</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.001615736840771982</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.867646821589003</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.001615736840771982</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.867646821589003</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.001660348889131583</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.001660348889131583</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.002929563088640184</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.002929563088640184</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.003979457252715852</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.003979457252715852</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.004882661054625831</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.004882661054625831</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.1140435692822802</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.005678899156948144</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.005678899156948144</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.003200672557362089</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.003200672557362089</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.005647350532318428</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.005647350532318428</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.007671242896801643</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.007671242896801643</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.009412358659519674</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.009412358659519674</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.2198430251224679</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.01094727548327353</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.01094727548327353</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>4.427597037684223e-05</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4.427597037684223e-05</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>7.812168236373825e-05</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>7.812168236373825e-05</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.0001061188600724227</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0001061188600724227</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="F35" t="n">
-        <v>7.773272235336725e-05</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.0001302042947900221</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.0001302042947900221</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Ichertswil</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="F36" t="n">
-        <v>7.773272235336725e-05</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.003041161847527472</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.0001514373108519505</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.0001514373108519505</v>
       </c>
     </row>
   </sheetData>
